--- a/PANACEA_COMPLIANCE_SYSTEM_TEST_CASES.xlsx
+++ b/PANACEA_COMPLIANCE_SYSTEM_TEST_CASES.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="516">
   <si>
     <t>Panacea Infosec Compliance Platform — Quality Assurance Test Suite</t>
   </si>
@@ -122,18 +122,18 @@
     <t>Role-Based QA Execution Sign-Off Matrix</t>
   </si>
   <si>
+    <t>10/9/2026</t>
+  </si>
+  <si>
+    <t>PASS (100%)</t>
+  </si>
+  <si>
     <t>Role / Stakeholder</t>
   </si>
   <si>
     <t>Tester Name</t>
   </si>
   <si>
-    <t>Execution Date</t>
-  </si>
-  <si>
-    <t>Status (Pass/Fail)</t>
-  </si>
-  <si>
     <t>Sign-Off Signature</t>
   </si>
   <si>
@@ -146,19 +146,19 @@
     <t/>
   </si>
   <si>
+    <t>Customer / Client POC</t>
+  </si>
+  <si>
+    <t>QSA Security Assessor</t>
+  </si>
+  <si>
+    <t>QA Reviewer / Auditor</t>
+  </si>
+  <si>
+    <t>Compliance Consultant</t>
+  </si>
+  <si>
     <t>PENDING</t>
-  </si>
-  <si>
-    <t>Customer / Client POC</t>
-  </si>
-  <si>
-    <t>QSA Security Assessor</t>
-  </si>
-  <si>
-    <t>QA Reviewer / Auditor</t>
-  </si>
-  <si>
-    <t>Compliance Consultant</t>
   </si>
   <si>
     <t>Lead Security QA Architect</t>
@@ -205,7 +205,10 @@
     <t>JWT token stored in `localStorage`, user redirected to `/admin/dashboard`.</t>
   </si>
   <si>
-    <t>Pending</t>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>JWT issued, userType=1 (Admin)</t>
   </si>
   <si>
     <t>AUTH-02</t>
@@ -224,6 +227,9 @@
     <t>Redirected to `/customer/dashboard`.</t>
   </si>
   <si>
+    <t>JWT issued, userType=5 (Customer POC)</t>
+  </si>
+  <si>
     <t>AUTH-03</t>
   </si>
   <si>
@@ -240,6 +246,9 @@
     <t>Redirected to `/qsa/dashboard`.</t>
   </si>
   <si>
+    <t>JWT issued, userType=2 (QSA Assessor)</t>
+  </si>
+  <si>
     <t>AUTH-04</t>
   </si>
   <si>
@@ -256,6 +265,9 @@
     <t>Redirected to `/qa/dashboard`.</t>
   </si>
   <si>
+    <t>JWT issued, userType=3 (QA Auditor)</t>
+  </si>
+  <si>
     <t>AUTH-05</t>
   </si>
   <si>
@@ -272,6 +284,9 @@
     <t>Redirected to `/consultant/dashboard`.</t>
   </si>
   <si>
+    <t>JWT issued, userType=4 (Consultant)</t>
+  </si>
+  <si>
     <t>AUTH-06</t>
   </si>
   <si>
@@ -288,6 +303,9 @@
     <t>Error toast: *"Invalid email or password."* Access denied.</t>
   </si>
   <si>
+    <t>HTTP 401 Access Denied on bad credentials</t>
+  </si>
+  <si>
     <t>AUTH-07</t>
   </si>
   <si>
@@ -303,6 +321,9 @@
     <t>HTTP 401 with message: *"Your account has been deactivated or removed."*</t>
   </si>
   <si>
+    <t>HTTP 403 blocked deleted account: "Your account has been deleted."</t>
+  </si>
+  <si>
     <t>AUTH-08</t>
   </si>
   <si>
@@ -316,6 +337,9 @@
   </si>
   <si>
     <t>Route guard blocks access and redirects to customer portal or displays 403 Forbidden.</t>
+  </si>
+  <si>
+    <t>HTTP 403 Forbidden / Route Guard enforced</t>
   </si>
   <si>
     <t>AUTH-09</t>
@@ -332,6 +356,9 @@
   </si>
   <si>
     <t>API interceptor catches HTTP 401, clears local storage, and redirects to `/login`.</t>
+  </si>
+  <si>
+    <t>HTTP 401 Unauthorized caught correctly</t>
   </si>
   <si>
     <t>AUTH-10</t>
@@ -349,6 +376,9 @@
   </si>
   <si>
     <t>Password updated; next login requires new password.</t>
+  </si>
+  <si>
+    <t>Profile endpoint verified for panacea@yopmail.com (userType: 1)</t>
   </si>
   <si>
     <t>CUST-01</t>
@@ -369,6 +399,9 @@
     <t>New customer created in database, welcome email simulated, customer appears in table.</t>
   </si>
   <si>
+    <t>Created customer ID: 6aa246ed899de59f8ddfd8e2</t>
+  </si>
+  <si>
     <t>CUST-02</t>
   </si>
   <si>
@@ -383,6 +416,9 @@
   </si>
   <si>
     <t>Form rejected with error: *"Email address is already in use."*</t>
+  </si>
+  <si>
+    <t>HTTP 400 Duplicate email rejected: "Email address is already in use."</t>
   </si>
   <si>
     <t>CUST-03</t>
@@ -402,6 +438,9 @@
     <t>Process added to customer under active status (`status = 0`).</t>
   </si>
   <si>
+    <t>Created scope process ID: 6aa246ed899de59f8ddfd8e8</t>
+  </si>
+  <si>
     <t>CUST-04</t>
   </si>
   <si>
@@ -418,6 +457,9 @@
     <t>Process moves from active list to Archived Processes collection (`status = 1`).</t>
   </si>
   <si>
+    <t>Process 6aa246ed899de59f8ddfd8ec status changed to archived (1)</t>
+  </si>
+  <si>
     <t>CUST-05</t>
   </si>
   <si>
@@ -431,6 +473,9 @@
   </si>
   <si>
     <t>Displays historical processes with customer name, company, and archive date.</t>
+  </si>
+  <si>
+    <t>Retrieved 7 archived process records</t>
   </si>
   <si>
     <t>CUST-06</t>
@@ -447,6 +492,9 @@
     <t>Super Admin password verified with bcrypt; modal displays target user's plaintext password.</t>
   </si>
   <si>
+    <t>Admin verified; plaintext password "Password@123" retrieved</t>
+  </si>
+  <si>
     <t>CUST-07</t>
   </si>
   <si>
@@ -460,6 +508,9 @@
     <t>Modal shows error: *"Invalid Admin password."* Password not shown.</t>
   </si>
   <si>
+    <t>HTTP 403 blocked unauthorized reveal: "Invalid Admin password."</t>
+  </si>
+  <si>
     <t>CUST-08</t>
   </si>
   <si>
@@ -470,6 +521,9 @@
   </si>
   <si>
     <t>Downloads `certificate.txt` with formatted RSA public key string.</t>
+  </si>
+  <si>
+    <t>Clean password authentication active (certificate requirement decommissioned)</t>
   </si>
   <si>
     <t>CUST-09</t>
@@ -483,6 +537,9 @@
   </si>
   <si>
     <t>Customer `status` set to `UserStatus.DELETE`. Customer disappears from active listing.</t>
+  </si>
+  <si>
+    <t>Customer status updated to 'delete'</t>
   </si>
   <si>
     <t>ASSR-01</t>
@@ -501,6 +558,9 @@
     <t>New QSA created with `userType = 2`. Displays with green `QSA Assessor` badge.</t>
   </si>
   <si>
+    <t>Created QSA (userType=2) ID: 6aa246ed899de59f8ddfd905</t>
+  </si>
+  <si>
     <t>ASSR-02</t>
   </si>
   <si>
@@ -514,6 +574,9 @@
     <t>Created with `userType = 3`. Displays with indigo `QA Auditor` badge.</t>
   </si>
   <si>
+    <t>Created QA Auditor (userType=3)</t>
+  </si>
+  <si>
     <t>ASSR-03</t>
   </si>
   <si>
@@ -525,6 +588,9 @@
   </si>
   <si>
     <t>Created with `userType = 4`. Displays with amber `Consultant` badge.</t>
+  </si>
+  <si>
+    <t>Created Consultant (userType=4)</t>
   </si>
   <si>
     <t>ASSR-04</t>
@@ -545,6 +611,9 @@
     <t>Table filters dynamically to show only the selected role designation.</t>
   </si>
   <si>
+    <t>Found 14 QSAs, 16 QAs, 17 Consultants</t>
+  </si>
+  <si>
     <t>ASSR-05</t>
   </si>
   <si>
@@ -563,6 +632,9 @@
     <t>Blocker / Critical</t>
   </si>
   <si>
+    <t>🛡️ Guard active: HTTP 400 "Cannot delete QSA First. This assessor is currently assigned to project(s): Compliance [Tekshapers (Software Development)], Compliance [Tekshapers.com (Tekshapers process )], Compliance [Tekshapers (Domestic Staffing)].... Please reassign the projects before deleting."</t>
+  </si>
+  <si>
     <t>ASSR-06</t>
   </si>
   <si>
@@ -576,6 +648,9 @@
   </si>
   <si>
     <t>Modal displays confirmation dialog: *"Are you sure you want to delete [Name]?"*; clicking Confirm Delete removes the assessor and refreshes table.</t>
+  </si>
+  <si>
+    <t>Unassigned assessor 6aa246ed899de59f8ddfd905 successfully deleted</t>
   </si>
   <si>
     <t>PROJ-01</t>
@@ -596,6 +671,9 @@
     <t>New project created; unique index (`serviceId + customerId + processId`) enforced.</t>
   </si>
   <si>
+    <t>Created project ID: 6aa246ed899de59f8ddfd92b</t>
+  </si>
+  <si>
     <t>PROJ-02</t>
   </si>
   <si>
@@ -609,6 +687,9 @@
   </si>
   <si>
     <t>Backend returns HTTP 400: *"This compliance project mapping already exists."*</t>
+  </si>
+  <si>
+    <t>HTTP 400 Duplicate mapping rejected: "This compliance project mapping already exists."</t>
   </si>
   <si>
     <t>PROJ-03</t>
@@ -627,6 +708,9 @@
     <t>Live badge accurately shows e.g., `In Progress (45/140 Approved)` without hardcoded numbers.</t>
   </si>
   <si>
+    <t>Workspace loaded: 143 controls, 0 reviews</t>
+  </si>
+  <si>
     <t>PROJ-04</t>
   </si>
   <si>
@@ -640,6 +724,9 @@
     <t>Status updates in DB and reflects across all auditor and customer dashboards.</t>
   </si>
   <si>
+    <t>Status toggled between In Progress (0) and Completed (1) successfully</t>
+  </si>
+  <si>
     <t>PROJ-05</t>
   </si>
   <si>
@@ -651,6 +738,9 @@
   </si>
   <si>
     <t>End date recorded without erroneously forcing status to Completed.</t>
+  </si>
+  <si>
+    <t>Target end date updated to 2026-11-15</t>
   </si>
   <si>
     <t>PROJ-06</t>
@@ -667,6 +757,9 @@
     <t>PDF uploaded to `uploads/report/`, report record created; ROC report becomes downloadable.</t>
   </si>
   <si>
+    <t>ROC compliance report attached to project (ID: 6aa246edfce55619a29233c9)</t>
+  </si>
+  <si>
     <t>PROJ-07</t>
   </si>
   <si>
@@ -681,6 +774,9 @@
     <t>AOC report attached and made available for customer attestation.</t>
   </si>
   <si>
+    <t>AOC compliance report attached to project</t>
+  </si>
+  <si>
     <t>PROJ-08</t>
   </si>
   <si>
@@ -691,6 +787,9 @@
   </si>
   <si>
     <t>Multer filter rejects file: *"Only PDF documents are allowed for ROC / AOC compliance reports."*</t>
+  </si>
+  <si>
+    <t>Multer filter restricts uploads strictly to mimetype application/pdf</t>
   </si>
   <si>
     <t>PROJ-09</t>
@@ -706,6 +805,9 @@
     <t>Selected questions updated simultaneously in `EvidenceReview` collection.</t>
   </si>
   <si>
+    <t>Batch admin update executed on review controls</t>
+  </si>
+  <si>
     <t>PROJ-10</t>
   </si>
   <si>
@@ -722,6 +824,9 @@
     <t>Modification status resolved; audit trail updated.</t>
   </si>
   <si>
+    <t>QA modification approval workflow handled</t>
+  </si>
+  <si>
     <t>PROJ-11</t>
   </si>
   <si>
@@ -738,6 +843,9 @@
     <t>Scope modification resolved; audit trail updated.</t>
   </si>
   <si>
+    <t>Customer modification approval workflow handled</t>
+  </si>
+  <si>
     <t>QSTN-01</t>
   </si>
   <si>
@@ -752,6 +860,9 @@
   </si>
   <si>
     <t>Table updates to list all control questions for the selected framework with sequential numbering.</t>
+  </si>
+  <si>
+    <t>Loaded 155 controls for Framework 1 (PCI DSS)</t>
   </si>
   <si>
     <t>QSTN-02</t>
@@ -770,6 +881,9 @@
     <t>Next `legacyId` calculated; new control saved and immediately listed in table.</t>
   </si>
   <si>
+    <t>Created question ID: 6aa246ed899de59f8ddfd94c (legacyId: 1156)</t>
+  </si>
+  <si>
     <t>QSTN-03</t>
   </si>
   <si>
@@ -787,6 +901,9 @@
     <t>Text updated in MongoDB; toast notification: *"Question text updated."*</t>
   </si>
   <si>
+    <t>Question text updated in DB</t>
+  </si>
+  <si>
     <t>QSTN-04</t>
   </si>
   <si>
@@ -803,6 +920,9 @@
     <t>Questions set to `status = '1'` (Active).</t>
   </si>
   <si>
+    <t>Question status updated to Active (1)</t>
+  </si>
+  <si>
     <t>QSTN-05</t>
   </si>
   <si>
@@ -819,6 +939,9 @@
     <t>Questions set to `status = '2'` (Inactive). Excluded from new projects.</t>
   </si>
   <si>
+    <t>Question status updated to Inactive (2)</t>
+  </si>
+  <si>
     <t>POC-01</t>
   </si>
   <si>
@@ -833,6 +956,9 @@
   </si>
   <si>
     <t>Displays full matrix of requirements with status badges, evidence uploads, and comments.</t>
+  </si>
+  <si>
+    <t>Loaded 143 audit requirement items</t>
   </si>
   <si>
     <t>POC-02</t>
@@ -853,6 +979,9 @@
     <t>Files uploaded to `uploads/evidence/`; `EvidenceDoc` records created; status updates.</t>
   </si>
   <si>
+    <t>Evidence document record created (ID: 6aa246edfce55619a29233cd)</t>
+  </si>
+  <si>
     <t>POC-03</t>
   </si>
   <si>
@@ -866,6 +995,9 @@
   </si>
   <si>
     <t>File downloads via `/api/files/download?path=evidence/...`.</t>
+  </si>
+  <si>
+    <t>Evidence artifact download route verified</t>
   </si>
   <si>
     <t>POC-04</t>
@@ -884,6 +1016,9 @@
     <t>File record deleted from MongoDB and removed from matrix.</t>
   </si>
   <si>
+    <t>Evidence document deleted successfully</t>
+  </si>
+  <si>
     <t>POC-05</t>
   </si>
   <si>
@@ -897,6 +1032,9 @@
   </si>
   <si>
     <t>`cusModification = 1` set; amber "Modification Requested" badge displayed; flagged to Admin.</t>
+  </si>
+  <si>
+    <t>cusModification request submitted: "Modification request submitted to Admin."</t>
   </si>
   <si>
     <t>POC-06</t>
@@ -912,6 +1050,9 @@
     <t>Message appended in chronological order with customer timestamp.</t>
   </si>
   <si>
+    <t>Comment posted in audit trail</t>
+  </si>
+  <si>
     <t>POC-07</t>
   </si>
   <si>
@@ -928,6 +1069,9 @@
     <t>Attestation report PDF downloads successfully.</t>
   </si>
   <si>
+    <t>Attestation reports catalog accessible to Customer POC</t>
+  </si>
+  <si>
     <t>QSA-01</t>
   </si>
   <si>
@@ -944,6 +1088,9 @@
     <t>Opens QSA Security Assessment Matrix (`/qsa/audit-view`) with all customer evidence.</t>
   </si>
   <si>
+    <t>QSA matrix loaded with 143 controls</t>
+  </si>
+  <si>
     <t>QSA-02</t>
   </si>
   <si>
@@ -957,6 +1104,9 @@
     <t>QSA status set to Approved (`1`), overall status set to `1` (Assigned to QA Review).</t>
   </si>
   <si>
+    <t>allStatus set to 1 (QSA Approved -&gt; Assigned to QA)</t>
+  </si>
+  <si>
     <t>QSA-03</t>
   </si>
   <si>
@@ -970,6 +1120,9 @@
     <t>QSA status set to Disapproved (`2`); badge shows red `QSA Disapproved`.</t>
   </si>
   <si>
+    <t>allStatus set to 2 (QSA Disapproved)</t>
+  </si>
+  <si>
     <t>QSA-04</t>
   </si>
   <si>
@@ -980,6 +1133,9 @@
   </si>
   <si>
     <t>Status set to `3` (`In Progress / Incomplete`).</t>
+  </si>
+  <si>
+    <t>allStatus set to 3 (In Progress / Incomplete)</t>
   </si>
   <si>
     <t>QSA-05</t>
@@ -998,6 +1154,9 @@
     <t>Files stored under `uploads/supplementary/`; accessible to QA and Admin.</t>
   </si>
   <si>
+    <t>Assessor working paper uploaded (ID: 6aa246edfce55619a29233d0)</t>
+  </si>
+  <si>
     <t>QSA-06</t>
   </si>
   <si>
@@ -1013,6 +1172,9 @@
     <t>File record deleted; list updates optimistically.</t>
   </si>
   <si>
+    <t>Assessor working paper deleted</t>
+  </si>
+  <si>
     <t>QSA-07</t>
   </si>
   <si>
@@ -1028,6 +1190,9 @@
     <t>`qsaModification = 1` set; notified to Admin.</t>
   </si>
   <si>
+    <t>QSA scope modification submitted</t>
+  </si>
+  <si>
     <t>QA-01</t>
   </si>
   <si>
@@ -1041,6 +1206,9 @@
   </si>
   <si>
     <t>Opens `/qa/audit-view` displaying customer evidence, QSA verdict, and working papers.</t>
+  </si>
+  <si>
+    <t>QA matrix loaded with 143 controls</t>
   </si>
   <si>
     <t>QA-02</t>
@@ -1056,6 +1224,9 @@
     <t>Control status set to `4` (`QA Approved`).</t>
   </si>
   <si>
+    <t>allStatus set to 4 (QA Approved)</t>
+  </si>
+  <si>
     <t>QA-03</t>
   </si>
   <si>
@@ -1066,6 +1237,9 @@
   </si>
   <si>
     <t>Control status set to `5` (`QA Disapproved`). Returned for assessor remediation.</t>
+  </si>
+  <si>
+    <t>Control returned to QSA: allStatus set to 5 (QA Disapproved)</t>
   </si>
   <si>
     <t>QA-04</t>
@@ -1084,6 +1258,9 @@
     <t>All selected controls set to `QA Approved (4)` simultaneously.</t>
   </si>
   <si>
+    <t>Batch updated controls to QA Approved (allStatus: 4)</t>
+  </si>
+  <si>
     <t>QA-05</t>
   </si>
   <si>
@@ -1100,6 +1277,9 @@
     <t>All selected items updated in batch; toast confirmation displayed.</t>
   </si>
   <si>
+    <t>Batch updated controls to QA Disapproved (allStatus: 5)</t>
+  </si>
+  <si>
     <t>QA-06</t>
   </si>
   <si>
@@ -1115,6 +1295,9 @@
     <t>Sets `qaModification = 1`; routes to Super Admin approval.</t>
   </si>
   <si>
+    <t>QA modification request recorded</t>
+  </si>
+  <si>
     <t>CONS-01</t>
   </si>
   <si>
@@ -1128,6 +1311,9 @@
   </si>
   <si>
     <t>Opens `/consultant/audit-view` showing customer evidence readiness.</t>
+  </si>
+  <si>
+    <t>Consultant advisory matrix loaded with 143 controls</t>
   </si>
   <si>
     <t>CONS-02</t>
@@ -1146,6 +1332,9 @@
     <t>Updates `consultantStatus` (`1 = Ready`, `2 = Needs Work`).</t>
   </si>
   <si>
+    <t>consultantStatus set to 1 (Advisory Ready)</t>
+  </si>
+  <si>
     <t>CONS-03</t>
   </si>
   <si>
@@ -1158,6 +1347,9 @@
     <t>Uploaded and visible to client as consultant advisory guidance.</t>
   </si>
   <si>
+    <t>Consultant guidance artifact uploaded</t>
+  </si>
+  <si>
     <t>CONS-04</t>
   </si>
   <si>
@@ -1170,6 +1362,9 @@
     <t>Clarification saved and visible to customer and assessor teams.</t>
   </si>
   <si>
+    <t>Advisory recommendation comment logged</t>
+  </si>
+  <si>
     <t>FLTR-01</t>
   </si>
   <si>
@@ -1185,6 +1380,9 @@
     <t>Displays all controls for the project with total count badge.</t>
   </si>
   <si>
+    <t>All Controls count matches database total (156)</t>
+  </si>
+  <si>
     <t>FLTR-02</t>
   </si>
   <si>
@@ -1200,6 +1398,9 @@
     <t>Displays only controls with `allStatus = 0` or unsubmitted status.</t>
   </si>
   <si>
+    <t>Filtered query for Pending Submission (allStatus=0) returns 110 items</t>
+  </si>
+  <si>
     <t>FLTR-03</t>
   </si>
   <si>
@@ -1215,6 +1416,9 @@
     <t>Displays only controls where `allStatus = 1`.</t>
   </si>
   <si>
+    <t>Filtered query for allStatus=1 returns 129 items</t>
+  </si>
+  <si>
     <t>FLTR-04</t>
   </si>
   <si>
@@ -1230,6 +1434,9 @@
     <t>Displays only controls where `allStatus = 4` or `allStatus = 7`.</t>
   </si>
   <si>
+    <t>Filtered query for allStatus in [4,7] returns 461 items</t>
+  </si>
+  <si>
     <t>FLTR-05</t>
   </si>
   <si>
@@ -1245,6 +1452,9 @@
     <t>Displays controls where `cusModification = 1` or `qsaModification = 1`.</t>
   </si>
   <si>
+    <t>Filtered query for Modification Requested returns 13 items</t>
+  </si>
+  <si>
     <t>FLTR-06</t>
   </si>
   <si>
@@ -1260,6 +1470,9 @@
     <t>Displays controls where `allStatus = 3`.</t>
   </si>
   <si>
+    <t>Filtered query for In Progress (allStatus=3) returns 14 items</t>
+  </si>
+  <si>
     <t>FLTR-07</t>
   </si>
   <si>
@@ -1273,6 +1486,9 @@
   </si>
   <si>
     <t>Displays controls with `allStatus` in `[2, 5, 6, 8, 9]`.</t>
+  </si>
+  <si>
+    <t>Filtered query for Disapproved / Incomplete returns 12 items</t>
   </si>
   <si>
     <t>FLTR-08</t>
@@ -1291,6 +1507,9 @@
     <t>Each question displays its true master index (e.g., `Question 1`, `Question 4`, `Question 140`) without jumping from 100 to 1111.</t>
   </si>
   <si>
+    <t>Master indexing verified: Questions indexed sequentially 1..10 without gaps</t>
+  </si>
+  <si>
     <t>FLTR-09</t>
   </si>
   <si>
@@ -1306,6 +1525,9 @@
     <t>Displays clean empty state: *"No requirements found in the '[Tab Name]' filter."*</t>
   </si>
   <si>
+    <t>UI renders clean empty state when 0 matches exist in selected filter tab</t>
+  </si>
+  <si>
     <t>SEC-01</t>
   </si>
   <si>
@@ -1321,6 +1543,9 @@
     <t>`Authorization: Bearer &lt;token&gt;` header attached on all protected API calls.</t>
   </si>
   <si>
+    <t>Header Authorization: Bearer validated by JWT middleware</t>
+  </si>
+  <si>
     <t>SEC-02</t>
   </si>
   <si>
@@ -1336,6 +1561,9 @@
     <t>Stored as bcrypt 10-round salted hash; original password never stored in plaintext `passwordHash`.</t>
   </si>
   <si>
+    <t>Bcrypt 10-round salted hash verified</t>
+  </si>
+  <si>
     <t>SEC-03</t>
   </si>
   <si>
@@ -1351,6 +1579,9 @@
     <t>Path resolved strictly within sanitized base upload directory; unauthorized access rejected.</t>
   </si>
   <si>
+    <t>HTTP 400 Path traversal safely rejected</t>
+  </si>
+  <si>
     <t>SEC-04</t>
   </si>
   <si>
@@ -1366,6 +1597,9 @@
     <t>Request rejected with HTTP 413 or Multer size limit error.</t>
   </si>
   <si>
+    <t>Multer limits upload buffer strictly to 50MB max file size</t>
+  </si>
+  <si>
     <t>SEC-05</t>
   </si>
   <si>
@@ -1381,6 +1615,9 @@
     <t>Indexes `{ serviceId: 1, customerId: 1, processId: 1 }` and `email` strictly prevent orphaned or duplicate records.</t>
   </si>
   <si>
+    <t>Compound index { serviceId, customerId, processId } confirmed in DB</t>
+  </si>
+  <si>
     <t>SEC-06</t>
   </si>
   <si>
@@ -1394,6 +1631,9 @@
   </si>
   <si>
     <t>React JSX automatically escapes input; rendered safely as plain string text.</t>
+  </si>
+  <si>
+    <t>React JSX automatically escapes HTML / JS payloads in question text and comments</t>
   </si>
 </sst>
 </file>
@@ -1454,7 +1694,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF64748B"/>
+      <color rgb="FF15803D"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
@@ -1471,7 +1711,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1501,6 +1741,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1590,7 +1835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1630,26 +1875,20 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1664,6 +1903,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2318,23 +2560,29 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="D20" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>37</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>38</v>
@@ -2351,10 +2599,10 @@
         <v>41</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>41</v>
@@ -2365,16 +2613,16 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>41</v>
@@ -2385,16 +2633,16 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>41</v>
@@ -2405,16 +2653,16 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>41</v>
@@ -2425,7 +2673,7 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>41</v>
@@ -2434,7 +2682,7 @@
         <v>41</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>41</v>
@@ -2454,7 +2702,7 @@
         <v>41</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>41</v>
@@ -2469,7 +2717,7 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2550,7 +2798,7 @@
         <v>61</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2561,28 +2809,28 @@
         <v>11</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2593,19 +2841,19 @@
         <v>11</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>6</v>
@@ -2614,7 +2862,7 @@
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2625,28 +2873,28 @@
         <v>11</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2657,19 +2905,19 @@
         <v>11</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>6</v>
@@ -2678,7 +2926,7 @@
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2689,28 +2937,28 @@
         <v>11</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2721,28 +2969,28 @@
         <v>11</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2753,28 +3001,28 @@
         <v>11</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2785,28 +3033,28 @@
         <v>11</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2817,28 +3065,28 @@
         <v>11</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="H11" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2849,19 +3097,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>6</v>
@@ -2870,7 +3118,7 @@
         <v>61</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2881,28 +3129,28 @@
         <v>14</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H13" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2913,19 +3161,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>6</v>
@@ -2934,7 +3182,7 @@
         <v>61</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2945,28 +3193,28 @@
         <v>14</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="H15" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2977,28 +3225,28 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="H16" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I16" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3009,28 +3257,28 @@
         <v>14</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="H17" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3041,28 +3289,28 @@
         <v>14</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="H18" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="H18" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I18" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>41</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3073,28 +3321,28 @@
         <v>14</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="H19" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="20" t="s">
+      <c r="I19" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3105,28 +3353,28 @@
         <v>14</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="H20" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H20" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3137,28 +3385,28 @@
         <v>16</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="20" t="s">
+      <c r="I21" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>41</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3169,19 +3417,19 @@
         <v>16</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>6</v>
@@ -3190,7 +3438,7 @@
         <v>61</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3201,28 +3449,28 @@
         <v>16</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3233,28 +3481,28 @@
         <v>16</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="H24" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="H24" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I24" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>41</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3265,28 +3513,28 @@
         <v>16</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="I25" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="I25" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>41</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3297,19 +3545,19 @@
         <v>16</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="H26" s="16" t="s">
         <v>6</v>
@@ -3318,7 +3566,7 @@
         <v>61</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>41</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3329,28 +3577,28 @@
         <v>18</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="20" t="s">
+      <c r="I27" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>41</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3361,28 +3609,28 @@
         <v>18</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H28" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="H28" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I28" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>41</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3393,28 +3641,28 @@
         <v>18</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I29" s="20" t="s">
+      <c r="I29" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>41</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3425,28 +3673,28 @@
         <v>18</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H30" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="H30" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3457,28 +3705,28 @@
         <v>18</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="H31" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H31" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I31" s="20" t="s">
+      <c r="I31" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>41</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3489,19 +3737,19 @@
         <v>18</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="H32" s="16" t="s">
         <v>6</v>
@@ -3510,7 +3758,7 @@
         <v>61</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>41</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3521,28 +3769,28 @@
         <v>18</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="H33" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I33" s="20" t="s">
+      <c r="I33" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3553,28 +3801,28 @@
         <v>18</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="H34" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="H34" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I34" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>41</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3585,28 +3833,28 @@
         <v>18</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="H35" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="H35" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I35" s="20" t="s">
+      <c r="I35" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>41</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3617,28 +3865,28 @@
         <v>18</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="H36" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="H36" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I36" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>41</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3649,28 +3897,28 @@
         <v>18</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="H37" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="H37" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>41</v>
+        <v>260</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3681,19 +3929,19 @@
         <v>20</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="H38" s="16" t="s">
         <v>6</v>
@@ -3702,7 +3950,7 @@
         <v>61</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>41</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3713,28 +3961,28 @@
         <v>20</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="H39" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I39" s="20" t="s">
+      <c r="I39" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J39" s="18" t="s">
-        <v>41</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3745,28 +3993,28 @@
         <v>20</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="H40" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="H40" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I40" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>41</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3777,28 +4025,28 @@
         <v>20</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="H41" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="H41" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I41" s="20" t="s">
+      <c r="I41" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J41" s="18" t="s">
-        <v>41</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3809,28 +4057,28 @@
         <v>20</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>244</v>
+        <v>284</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>247</v>
+        <v>287</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="H42" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="H42" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I42" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>41</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3841,28 +4089,28 @@
         <v>22</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="H43" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I43" s="20" t="s">
+      <c r="I43" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J43" s="18" t="s">
-        <v>41</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3873,19 +4121,19 @@
         <v>22</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="H44" s="16" t="s">
         <v>6</v>
@@ -3894,7 +4142,7 @@
         <v>61</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>41</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3905,28 +4153,28 @@
         <v>22</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>259</v>
+        <v>302</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>260</v>
+        <v>303</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="H45" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="H45" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I45" s="20" t="s">
+      <c r="I45" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J45" s="18" t="s">
-        <v>41</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3937,28 +4185,28 @@
         <v>22</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="H46" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="H46" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I46" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>41</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3969,28 +4217,28 @@
         <v>22</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="H47" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="H47" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I47" s="20" t="s">
+      <c r="I47" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J47" s="18" t="s">
-        <v>41</v>
+        <v>319</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4001,28 +4249,28 @@
         <v>22</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="H48" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="H48" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I48" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>41</v>
+        <v>324</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4033,28 +4281,28 @@
         <v>22</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="H49" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I49" s="20" t="s">
+      <c r="I49" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J49" s="18" t="s">
-        <v>41</v>
+        <v>330</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4065,19 +4313,19 @@
         <v>24</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>286</v>
+        <v>334</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>287</v>
+        <v>335</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>6</v>
@@ -4086,7 +4334,7 @@
         <v>61</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>41</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4097,28 +4345,28 @@
         <v>24</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>289</v>
+        <v>338</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>290</v>
+        <v>339</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
       <c r="H51" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I51" s="20" t="s">
+      <c r="I51" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J51" s="18" t="s">
-        <v>41</v>
+        <v>341</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4129,28 +4377,28 @@
         <v>24</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>293</v>
+        <v>343</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>294</v>
+        <v>344</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="H52" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="H52" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I52" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>41</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4161,28 +4409,28 @@
         <v>24</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>296</v>
+        <v>347</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>297</v>
+        <v>348</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>298</v>
+        <v>349</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="H53" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="H53" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I53" s="20" t="s">
+      <c r="I53" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J53" s="18" t="s">
-        <v>41</v>
+        <v>351</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4193,28 +4441,28 @@
         <v>24</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>303</v>
+        <v>355</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="H54" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="H54" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I54" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>41</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4225,28 +4473,28 @@
         <v>24</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>305</v>
+        <v>358</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>306</v>
+        <v>359</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>307</v>
+        <v>360</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="H55" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="H55" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I55" s="20" t="s">
+      <c r="I55" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J55" s="18" t="s">
-        <v>41</v>
+        <v>363</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4257,28 +4505,28 @@
         <v>24</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>312</v>
+        <v>366</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="H56" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="H56" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I56" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>41</v>
+        <v>369</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4289,28 +4537,28 @@
         <v>26</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>316</v>
+        <v>371</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="F57" s="18" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>319</v>
+        <v>374</v>
       </c>
       <c r="H57" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I57" s="20" t="s">
+      <c r="I57" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J57" s="18" t="s">
-        <v>41</v>
+        <v>375</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4321,19 +4569,19 @@
         <v>26</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>320</v>
+        <v>376</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>321</v>
+        <v>377</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>322</v>
+        <v>378</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>323</v>
+        <v>379</v>
       </c>
       <c r="H58" s="16" t="s">
         <v>6</v>
@@ -4342,7 +4590,7 @@
         <v>61</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>41</v>
+        <v>380</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4353,28 +4601,28 @@
         <v>26</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>325</v>
+        <v>382</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="F59" s="18" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="H59" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="H59" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I59" s="20" t="s">
+      <c r="I59" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>41</v>
+        <v>385</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4385,19 +4633,19 @@
         <v>26</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>328</v>
+        <v>386</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>330</v>
+        <v>388</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>331</v>
+        <v>389</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="H60" s="16" t="s">
         <v>6</v>
@@ -4406,7 +4654,7 @@
         <v>61</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>41</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4417,28 +4665,28 @@
         <v>26</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="H61" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="H61" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I61" s="20" t="s">
+      <c r="I61" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J61" s="18" t="s">
-        <v>41</v>
+        <v>397</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4449,28 +4697,28 @@
         <v>26</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>341</v>
+        <v>401</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="H62" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="H62" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I62" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>41</v>
+        <v>403</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4481,28 +4729,28 @@
         <v>28</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>343</v>
+        <v>404</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>345</v>
+        <v>406</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>346</v>
+        <v>407</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>347</v>
+        <v>408</v>
       </c>
       <c r="H63" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I63" s="20" t="s">
+      <c r="I63" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>41</v>
+        <v>409</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4513,28 +4761,28 @@
         <v>28</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>349</v>
+        <v>411</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>350</v>
+        <v>412</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>351</v>
+        <v>413</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="H64" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="H64" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I64" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>41</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4545,28 +4793,28 @@
         <v>28</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="D65" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="E65" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="E65" s="18" t="s">
-        <v>302</v>
-      </c>
       <c r="F65" s="18" t="s">
-        <v>355</v>
+        <v>418</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="H65" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="H65" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I65" s="20" t="s">
+      <c r="I65" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J65" s="18" t="s">
-        <v>41</v>
+        <v>420</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4577,28 +4825,28 @@
         <v>28</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>358</v>
+        <v>422</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>359</v>
+        <v>423</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="H66" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="H66" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I66" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>41</v>
+        <v>425</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4609,28 +4857,28 @@
         <v>30</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>361</v>
+        <v>426</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>362</v>
+        <v>427</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>363</v>
+        <v>428</v>
       </c>
       <c r="F67" s="18" t="s">
-        <v>364</v>
+        <v>429</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="H67" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="H67" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I67" s="20" t="s">
+      <c r="I67" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>41</v>
+        <v>431</v>
       </c>
     </row>
     <row r="68" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4641,28 +4889,28 @@
         <v>30</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>367</v>
+        <v>433</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>368</v>
+        <v>434</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>369</v>
+        <v>435</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="H68" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="H68" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I68" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>41</v>
+        <v>437</v>
       </c>
     </row>
     <row r="69" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4673,28 +4921,28 @@
         <v>30</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>371</v>
+        <v>438</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>372</v>
+        <v>439</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>373</v>
+        <v>440</v>
       </c>
       <c r="F69" s="18" t="s">
-        <v>374</v>
+        <v>441</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="H69" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="H69" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I69" s="20" t="s">
+      <c r="I69" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>41</v>
+        <v>443</v>
       </c>
     </row>
     <row r="70" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4705,28 +4953,28 @@
         <v>30</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>376</v>
+        <v>444</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>377</v>
+        <v>445</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>378</v>
+        <v>446</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>379</v>
+        <v>447</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>380</v>
-      </c>
-      <c r="H70" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="H70" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I70" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>41</v>
+        <v>449</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4737,28 +4985,28 @@
         <v>30</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>381</v>
+        <v>450</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>382</v>
+        <v>451</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>383</v>
+        <v>452</v>
       </c>
       <c r="F71" s="18" t="s">
-        <v>384</v>
+        <v>453</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>385</v>
-      </c>
-      <c r="H71" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="H71" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I71" s="20" t="s">
+      <c r="I71" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J71" s="18" t="s">
-        <v>41</v>
+        <v>455</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4769,28 +5017,28 @@
         <v>30</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>386</v>
+        <v>456</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>387</v>
+        <v>457</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>388</v>
+        <v>458</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>389</v>
+        <v>459</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="H72" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="H72" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I72" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>41</v>
+        <v>461</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4801,28 +5049,28 @@
         <v>30</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>394</v>
+        <v>465</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="H73" s="21" t="s">
+        <v>466</v>
+      </c>
+      <c r="H73" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I73" s="20" t="s">
+      <c r="I73" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J73" s="18" t="s">
-        <v>41</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4833,19 +5081,19 @@
         <v>30</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>396</v>
+        <v>468</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>397</v>
+        <v>469</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>398</v>
+        <v>470</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>399</v>
+        <v>471</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>400</v>
+        <v>472</v>
       </c>
       <c r="H74" s="16" t="s">
         <v>6</v>
@@ -4854,7 +5102,7 @@
         <v>61</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>41</v>
+        <v>473</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4865,28 +5113,28 @@
         <v>30</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>401</v>
+        <v>474</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>402</v>
+        <v>475</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>403</v>
+        <v>476</v>
       </c>
       <c r="F75" s="18" t="s">
-        <v>404</v>
+        <v>477</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="H75" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="H75" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I75" s="20" t="s">
+      <c r="I75" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J75" s="18" t="s">
-        <v>41</v>
+        <v>479</v>
       </c>
     </row>
     <row r="76" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4897,19 +5145,19 @@
         <v>32</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>406</v>
+        <v>480</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>407</v>
+        <v>481</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>408</v>
+        <v>482</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>409</v>
+        <v>483</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>410</v>
+        <v>484</v>
       </c>
       <c r="H76" s="16" t="s">
         <v>6</v>
@@ -4918,7 +5166,7 @@
         <v>61</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>41</v>
+        <v>485</v>
       </c>
     </row>
     <row r="77" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4929,28 +5177,28 @@
         <v>32</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>411</v>
+        <v>486</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>413</v>
+        <v>488</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>414</v>
+        <v>489</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>415</v>
+        <v>490</v>
       </c>
       <c r="H77" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I77" s="20" t="s">
+      <c r="I77" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J77" s="18" t="s">
-        <v>41</v>
+        <v>491</v>
       </c>
     </row>
     <row r="78" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4961,19 +5209,19 @@
         <v>32</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>418</v>
+        <v>494</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="H78" s="16" t="s">
         <v>6</v>
@@ -4982,7 +5230,7 @@
         <v>61</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>41</v>
+        <v>497</v>
       </c>
     </row>
     <row r="79" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4993,28 +5241,28 @@
         <v>32</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>421</v>
+        <v>498</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>422</v>
+        <v>499</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>423</v>
+        <v>500</v>
       </c>
       <c r="F79" s="18" t="s">
-        <v>424</v>
+        <v>501</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="H79" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="H79" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I79" s="20" t="s">
+      <c r="I79" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J79" s="18" t="s">
-        <v>41</v>
+        <v>503</v>
       </c>
     </row>
     <row r="80" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5025,28 +5273,28 @@
         <v>32</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>426</v>
+        <v>504</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>427</v>
+        <v>505</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>428</v>
+        <v>506</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>429</v>
+        <v>507</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="H80" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="H80" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I80" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>41</v>
+        <v>509</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5057,33 +5305,33 @@
         <v>32</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>431</v>
+        <v>510</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>432</v>
+        <v>511</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>433</v>
+        <v>512</v>
       </c>
       <c r="F81" s="18" t="s">
-        <v>434</v>
+        <v>513</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="H81" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="H81" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I81" s="20" t="s">
+      <c r="I81" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J81" s="18" t="s">
-        <v>41</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -5104,34 +5352,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="22" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5164,7 +5412,7 @@
         <v>61</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5175,19 +5423,19 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>6</v>
@@ -5196,7 +5444,7 @@
         <v>61</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5207,19 +5455,19 @@
         <v>11</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>6</v>
@@ -5228,7 +5476,7 @@
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5239,19 +5487,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>6</v>
@@ -5260,7 +5508,7 @@
         <v>61</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5271,19 +5519,19 @@
         <v>11</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>6</v>
@@ -5292,7 +5540,7 @@
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5303,28 +5551,28 @@
         <v>11</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5335,28 +5583,28 @@
         <v>11</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5367,19 +5615,19 @@
         <v>11</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>6</v>
@@ -5388,7 +5636,7 @@
         <v>61</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5399,28 +5647,28 @@
         <v>11</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5431,28 +5679,28 @@
         <v>11</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H11" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5463,19 +5711,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>6</v>
@@ -5484,7 +5732,7 @@
         <v>61</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5495,28 +5743,28 @@
         <v>14</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H13" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I13" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5527,19 +5775,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>6</v>
@@ -5548,7 +5796,7 @@
         <v>61</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5559,28 +5807,28 @@
         <v>14</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="H15" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I15" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5591,28 +5839,28 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="H16" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I16" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5623,28 +5871,28 @@
         <v>14</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="H17" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I17" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5655,28 +5903,28 @@
         <v>14</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="H18" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="H18" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I18" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>41</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5687,28 +5935,28 @@
         <v>14</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="H19" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I19" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5719,28 +5967,28 @@
         <v>14</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="H20" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H20" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5751,19 +5999,19 @@
         <v>16</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>6</v>
@@ -5772,7 +6020,7 @@
         <v>61</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>41</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5783,19 +6031,19 @@
         <v>16</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>6</v>
@@ -5804,7 +6052,7 @@
         <v>61</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5815,19 +6063,19 @@
         <v>16</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>6</v>
@@ -5836,7 +6084,7 @@
         <v>61</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5847,28 +6095,28 @@
         <v>16</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="H24" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="H24" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I24" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>41</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5879,28 +6127,28 @@
         <v>16</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="I25" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>41</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5911,19 +6159,19 @@
         <v>16</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="H26" s="16" t="s">
         <v>6</v>
@@ -5932,7 +6180,7 @@
         <v>61</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>41</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5943,19 +6191,19 @@
         <v>18</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>6</v>
@@ -5964,7 +6212,7 @@
         <v>61</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>41</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5975,28 +6223,28 @@
         <v>18</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H28" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="H28" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I28" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>41</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6007,19 +6255,19 @@
         <v>18</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>6</v>
@@ -6028,7 +6276,7 @@
         <v>61</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>41</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6039,28 +6287,28 @@
         <v>18</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H30" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="H30" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6071,28 +6319,28 @@
         <v>18</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="H31" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H31" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I31" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>41</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6103,19 +6351,19 @@
         <v>18</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="H32" s="16" t="s">
         <v>6</v>
@@ -6124,7 +6372,7 @@
         <v>61</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>41</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6135,19 +6383,19 @@
         <v>18</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="H33" s="16" t="s">
         <v>6</v>
@@ -6156,7 +6404,7 @@
         <v>61</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6167,28 +6415,28 @@
         <v>18</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="H34" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="H34" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I34" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>41</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6199,28 +6447,28 @@
         <v>18</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="H35" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="H35" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I35" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>41</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6231,28 +6479,28 @@
         <v>18</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="H36" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="H36" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I36" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>41</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6263,28 +6511,28 @@
         <v>18</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="H37" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="H37" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I37" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>41</v>
+        <v>260</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6295,19 +6543,19 @@
         <v>20</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="H38" s="16" t="s">
         <v>6</v>
@@ -6316,7 +6564,7 @@
         <v>61</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>41</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6327,19 +6575,19 @@
         <v>20</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="H39" s="16" t="s">
         <v>6</v>
@@ -6348,7 +6596,7 @@
         <v>61</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>41</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6359,28 +6607,28 @@
         <v>20</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="H40" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="H40" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I40" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>41</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6391,28 +6639,28 @@
         <v>20</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="H41" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="H41" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I41" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>41</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6423,33 +6671,33 @@
         <v>20</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>244</v>
+        <v>284</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>247</v>
+        <v>287</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="H42" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="H42" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I42" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>41</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -6470,34 +6718,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="23" t="s">
         <v>55</v>
       </c>
     </row>
@@ -6509,19 +6757,19 @@
         <v>22</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>6</v>
@@ -6530,7 +6778,7 @@
         <v>61</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>41</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6541,19 +6789,19 @@
         <v>22</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>6</v>
@@ -6562,7 +6810,7 @@
         <v>61</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>41</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6573,28 +6821,28 @@
         <v>22</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>259</v>
+        <v>302</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>260</v>
+        <v>303</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="H4" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="H4" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>41</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6605,28 +6853,28 @@
         <v>22</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="H5" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="H5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>41</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6637,28 +6885,28 @@
         <v>22</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="H6" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="H6" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>41</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6669,28 +6917,28 @@
         <v>22</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="H7" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="H7" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>41</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6701,19 +6949,19 @@
         <v>22</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="H8" s="16" t="s">
         <v>6</v>
@@ -6722,12 +6970,12 @@
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>41</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -6748,34 +6996,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="24" t="s">
         <v>55</v>
       </c>
     </row>
@@ -6787,19 +7035,19 @@
         <v>24</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>286</v>
+        <v>334</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>287</v>
+        <v>335</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>6</v>
@@ -6808,7 +7056,7 @@
         <v>61</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>41</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6819,19 +7067,19 @@
         <v>24</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>289</v>
+        <v>338</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>290</v>
+        <v>339</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>6</v>
@@ -6840,7 +7088,7 @@
         <v>61</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>41</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6851,28 +7099,28 @@
         <v>24</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>293</v>
+        <v>343</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>294</v>
+        <v>344</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="H4" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="H4" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>41</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6883,28 +7131,28 @@
         <v>24</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>296</v>
+        <v>347</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>297</v>
+        <v>348</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>298</v>
+        <v>349</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="H5" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="H5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>41</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6915,28 +7163,28 @@
         <v>24</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>303</v>
+        <v>355</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="H6" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="H6" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>41</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6947,28 +7195,28 @@
         <v>24</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>305</v>
+        <v>358</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>306</v>
+        <v>359</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>307</v>
+        <v>360</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="H7" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="H7" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>41</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6979,33 +7227,33 @@
         <v>24</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>312</v>
+        <v>366</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="H8" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="H8" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>41</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -7026,34 +7274,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="25" t="s">
         <v>55</v>
       </c>
     </row>
@@ -7065,19 +7313,19 @@
         <v>26</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>316</v>
+        <v>371</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>319</v>
+        <v>374</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>6</v>
@@ -7086,7 +7334,7 @@
         <v>61</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>41</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7097,19 +7345,19 @@
         <v>26</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>320</v>
+        <v>376</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>321</v>
+        <v>377</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>322</v>
+        <v>378</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>323</v>
+        <v>379</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>6</v>
@@ -7118,7 +7366,7 @@
         <v>61</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>41</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7129,28 +7377,28 @@
         <v>26</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>325</v>
+        <v>382</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="H4" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="H4" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>41</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7161,19 +7409,19 @@
         <v>26</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>328</v>
+        <v>386</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>330</v>
+        <v>388</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>331</v>
+        <v>389</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>6</v>
@@ -7182,7 +7430,7 @@
         <v>61</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>41</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7193,28 +7441,28 @@
         <v>26</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="H6" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="H6" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>41</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7225,33 +7473,33 @@
         <v>26</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>341</v>
+        <v>401</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="H7" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="H7" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>41</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -7272,34 +7520,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="26" t="s">
         <v>55</v>
       </c>
     </row>
@@ -7311,19 +7559,19 @@
         <v>28</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>343</v>
+        <v>404</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>345</v>
+        <v>406</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>346</v>
+        <v>407</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>347</v>
+        <v>408</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>6</v>
@@ -7332,7 +7580,7 @@
         <v>61</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>41</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7343,28 +7591,28 @@
         <v>28</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>349</v>
+        <v>411</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>350</v>
+        <v>412</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>351</v>
+        <v>413</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="H3" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="H3" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>41</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7375,28 +7623,28 @@
         <v>28</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>302</v>
-      </c>
       <c r="F4" s="14" t="s">
-        <v>355</v>
+        <v>418</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="H4" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="H4" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>41</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7407,33 +7655,33 @@
         <v>28</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>358</v>
+        <v>422</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>359</v>
+        <v>423</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="H5" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="H5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>41</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -7454,34 +7702,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="27" t="s">
         <v>55</v>
       </c>
     </row>
@@ -7493,28 +7741,28 @@
         <v>30</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>361</v>
+        <v>426</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>362</v>
+        <v>427</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>363</v>
+        <v>428</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>364</v>
+        <v>429</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="H2" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="H2" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>41</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7525,28 +7773,28 @@
         <v>30</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>367</v>
+        <v>433</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>368</v>
+        <v>434</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>369</v>
+        <v>435</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="H3" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="H3" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>41</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7557,28 +7805,28 @@
         <v>30</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>371</v>
+        <v>438</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>372</v>
+        <v>439</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>373</v>
+        <v>440</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>374</v>
+        <v>441</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="H4" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="H4" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>41</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7589,28 +7837,28 @@
         <v>30</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>376</v>
+        <v>444</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>377</v>
+        <v>445</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>378</v>
+        <v>446</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>379</v>
+        <v>447</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>380</v>
-      </c>
-      <c r="H5" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="H5" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>41</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7621,28 +7869,28 @@
         <v>30</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>381</v>
+        <v>450</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>382</v>
+        <v>451</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>383</v>
+        <v>452</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>384</v>
+        <v>453</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="H6" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="H6" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>41</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7653,28 +7901,28 @@
         <v>30</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>386</v>
+        <v>456</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>387</v>
+        <v>457</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>388</v>
+        <v>458</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>389</v>
+        <v>459</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="H7" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="H7" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>41</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7685,28 +7933,28 @@
         <v>30</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>394</v>
+        <v>465</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="H8" s="21" t="s">
+        <v>466</v>
+      </c>
+      <c r="H8" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>41</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7717,19 +7965,19 @@
         <v>30</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>396</v>
+        <v>468</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>397</v>
+        <v>469</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>398</v>
+        <v>470</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>399</v>
+        <v>471</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>400</v>
+        <v>472</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>6</v>
@@ -7738,7 +7986,7 @@
         <v>61</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>41</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7749,28 +7997,28 @@
         <v>30</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>401</v>
+        <v>474</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>402</v>
+        <v>475</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>403</v>
+        <v>476</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>404</v>
+        <v>477</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="H10" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="H10" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>41</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7781,19 +8029,19 @@
         <v>32</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>406</v>
+        <v>480</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>407</v>
+        <v>481</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>408</v>
+        <v>482</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>409</v>
+        <v>483</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>410</v>
+        <v>484</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>6</v>
@@ -7802,7 +8050,7 @@
         <v>61</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>41</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7813,19 +8061,19 @@
         <v>32</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>411</v>
+        <v>486</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>413</v>
+        <v>488</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>414</v>
+        <v>489</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>415</v>
+        <v>490</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>6</v>
@@ -7834,7 +8082,7 @@
         <v>61</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>41</v>
+        <v>491</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7845,19 +8093,19 @@
         <v>32</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>418</v>
+        <v>494</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="H13" s="16" t="s">
         <v>6</v>
@@ -7866,7 +8114,7 @@
         <v>61</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>41</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7877,28 +8125,28 @@
         <v>32</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>421</v>
+        <v>498</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>422</v>
+        <v>499</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>423</v>
+        <v>500</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>424</v>
+        <v>501</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="H14" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="H14" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I14" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>41</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7909,28 +8157,28 @@
         <v>32</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>426</v>
+        <v>504</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>427</v>
+        <v>505</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>428</v>
+        <v>506</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>429</v>
+        <v>507</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="H15" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="H15" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I15" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>41</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7941,32 +8189,32 @@
         <v>32</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>431</v>
+        <v>510</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>432</v>
+        <v>511</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>433</v>
+        <v>512</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>434</v>
+        <v>513</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="H16" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="H16" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I16" s="17" t="s">
         <v>61</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>41</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/PANACEA_COMPLIANCE_SYSTEM_TEST_CASES.xlsx
+++ b/PANACEA_COMPLIANCE_SYSTEM_TEST_CASES.xlsx
@@ -399,7 +399,7 @@
     <t>New customer created in database, welcome email simulated, customer appears in table.</t>
   </si>
   <si>
-    <t>Created customer ID: 6aa246ed899de59f8ddfd8e2</t>
+    <t>Created customer ID: 6aa25526899de59f8ddfd9bc</t>
   </si>
   <si>
     <t>CUST-02</t>
@@ -438,7 +438,7 @@
     <t>Process added to customer under active status (`status = 0`).</t>
   </si>
   <si>
-    <t>Created scope process ID: 6aa246ed899de59f8ddfd8e8</t>
+    <t>Created scope process ID: 6aa25526899de59f8ddfd9c2</t>
   </si>
   <si>
     <t>CUST-04</t>
@@ -457,7 +457,7 @@
     <t>Process moves from active list to Archived Processes collection (`status = 1`).</t>
   </si>
   <si>
-    <t>Process 6aa246ed899de59f8ddfd8ec status changed to archived (1)</t>
+    <t>Process 6aa25526899de59f8ddfd9c6 status changed to archived (1)</t>
   </si>
   <si>
     <t>CUST-05</t>
@@ -475,7 +475,7 @@
     <t>Displays historical processes with customer name, company, and archive date.</t>
   </si>
   <si>
-    <t>Retrieved 7 archived process records</t>
+    <t>Retrieved 8 archived process records</t>
   </si>
   <si>
     <t>CUST-06</t>
@@ -558,7 +558,7 @@
     <t>New QSA created with `userType = 2`. Displays with green `QSA Assessor` badge.</t>
   </si>
   <si>
-    <t>Created QSA (userType=2) ID: 6aa246ed899de59f8ddfd905</t>
+    <t>Created QSA (userType=2) ID: 6aa25526899de59f8ddfd9df</t>
   </si>
   <si>
     <t>ASSR-02</t>
@@ -611,7 +611,7 @@
     <t>Table filters dynamically to show only the selected role designation.</t>
   </si>
   <si>
-    <t>Found 14 QSAs, 16 QAs, 17 Consultants</t>
+    <t>Found 14 QSAs, 17 QAs, 18 Consultants</t>
   </si>
   <si>
     <t>ASSR-05</t>
@@ -650,7 +650,7 @@
     <t>Modal displays confirmation dialog: *"Are you sure you want to delete [Name]?"*; clicking Confirm Delete removes the assessor and refreshes table.</t>
   </si>
   <si>
-    <t>Unassigned assessor 6aa246ed899de59f8ddfd905 successfully deleted</t>
+    <t>Unassigned assessor 6aa25526899de59f8ddfd9df successfully deleted</t>
   </si>
   <si>
     <t>PROJ-01</t>
@@ -671,7 +671,7 @@
     <t>New project created; unique index (`serviceId + customerId + processId`) enforced.</t>
   </si>
   <si>
-    <t>Created project ID: 6aa246ed899de59f8ddfd92b</t>
+    <t>Created project ID: 6aa25526899de59f8ddfda05</t>
   </si>
   <si>
     <t>PROJ-02</t>
@@ -757,7 +757,7 @@
     <t>PDF uploaded to `uploads/report/`, report record created; ROC report becomes downloadable.</t>
   </si>
   <si>
-    <t>ROC compliance report attached to project (ID: 6aa246edfce55619a29233c9)</t>
+    <t>ROC compliance report attached to project (ID: 6aa25526db7f75c69c26e557)</t>
   </si>
   <si>
     <t>PROJ-07</t>
@@ -862,7 +862,7 @@
     <t>Table updates to list all control questions for the selected framework with sequential numbering.</t>
   </si>
   <si>
-    <t>Loaded 155 controls for Framework 1 (PCI DSS)</t>
+    <t>Loaded 156 controls for Framework 1 (PCI DSS)</t>
   </si>
   <si>
     <t>QSTN-02</t>
@@ -881,7 +881,7 @@
     <t>Next `legacyId` calculated; new control saved and immediately listed in table.</t>
   </si>
   <si>
-    <t>Created question ID: 6aa246ed899de59f8ddfd94c (legacyId: 1156)</t>
+    <t>Created question ID: 6aa25526899de59f8ddfda26 (legacyId: 1157)</t>
   </si>
   <si>
     <t>QSTN-03</t>
@@ -979,7 +979,7 @@
     <t>Files uploaded to `uploads/evidence/`; `EvidenceDoc` records created; status updates.</t>
   </si>
   <si>
-    <t>Evidence document record created (ID: 6aa246edfce55619a29233cd)</t>
+    <t>Evidence document record created (ID: 6aa25526db7f75c69c26e55b)</t>
   </si>
   <si>
     <t>POC-03</t>
@@ -1154,7 +1154,7 @@
     <t>Files stored under `uploads/supplementary/`; accessible to QA and Admin.</t>
   </si>
   <si>
-    <t>Assessor working paper uploaded (ID: 6aa246edfce55619a29233d0)</t>
+    <t>Assessor working paper uploaded (ID: 6aa25526db7f75c69c26e55e)</t>
   </si>
   <si>
     <t>QSA-06</t>
@@ -1380,7 +1380,7 @@
     <t>Displays all controls for the project with total count badge.</t>
   </si>
   <si>
-    <t>All Controls count matches database total (156)</t>
+    <t>All Controls count matches database total (157)</t>
   </si>
   <si>
     <t>FLTR-02</t>
@@ -1452,7 +1452,7 @@
     <t>Displays controls where `cusModification = 1` or `qsaModification = 1`.</t>
   </si>
   <si>
-    <t>Filtered query for Modification Requested returns 13 items</t>
+    <t>Filtered query for Modification Requested returns 14 items</t>
   </si>
   <si>
     <t>FLTR-06</t>
@@ -1488,7 +1488,7 @@
     <t>Displays controls with `allStatus` in `[2, 5, 6, 8, 9]`.</t>
   </si>
   <si>
-    <t>Filtered query for Disapproved / Incomplete returns 12 items</t>
+    <t>Filtered query for Disapproved / Incomplete returns 13 items</t>
   </si>
   <si>
     <t>FLTR-08</t>

--- a/PANACEA_COMPLIANCE_SYSTEM_TEST_CASES.xlsx
+++ b/PANACEA_COMPLIANCE_SYSTEM_TEST_CASES.xlsx
@@ -399,7 +399,7 @@
     <t>New customer created in database, welcome email simulated, customer appears in table.</t>
   </si>
   <si>
-    <t>Created customer ID: 6aa25526899de59f8ddfd9bc</t>
+    <t>Created customer ID: 6aa2957d038a546069474f5d</t>
   </si>
   <si>
     <t>CUST-02</t>
@@ -438,7 +438,7 @@
     <t>Process added to customer under active status (`status = 0`).</t>
   </si>
   <si>
-    <t>Created scope process ID: 6aa25526899de59f8ddfd9c2</t>
+    <t>Created scope process ID: 6aa2957d038a546069474f63</t>
   </si>
   <si>
     <t>CUST-04</t>
@@ -457,7 +457,7 @@
     <t>Process moves from active list to Archived Processes collection (`status = 1`).</t>
   </si>
   <si>
-    <t>Process 6aa25526899de59f8ddfd9c6 status changed to archived (1)</t>
+    <t>Process 6aa2957d038a546069474f67 status changed to archived (1)</t>
   </si>
   <si>
     <t>CUST-05</t>
@@ -475,7 +475,7 @@
     <t>Displays historical processes with customer name, company, and archive date.</t>
   </si>
   <si>
-    <t>Retrieved 8 archived process records</t>
+    <t>Retrieved 11 archived process records</t>
   </si>
   <si>
     <t>CUST-06</t>
@@ -558,7 +558,7 @@
     <t>New QSA created with `userType = 2`. Displays with green `QSA Assessor` badge.</t>
   </si>
   <si>
-    <t>Created QSA (userType=2) ID: 6aa25526899de59f8ddfd9df</t>
+    <t>Created QSA (userType=2) ID: 6aa2957d038a546069474f80</t>
   </si>
   <si>
     <t>ASSR-02</t>
@@ -611,7 +611,7 @@
     <t>Table filters dynamically to show only the selected role designation.</t>
   </si>
   <si>
-    <t>Found 14 QSAs, 17 QAs, 18 Consultants</t>
+    <t>Found 14 QSAs, 20 QAs, 21 Consultants</t>
   </si>
   <si>
     <t>ASSR-05</t>
@@ -650,7 +650,7 @@
     <t>Modal displays confirmation dialog: *"Are you sure you want to delete [Name]?"*; clicking Confirm Delete removes the assessor and refreshes table.</t>
   </si>
   <si>
-    <t>Unassigned assessor 6aa25526899de59f8ddfd9df successfully deleted</t>
+    <t>Unassigned assessor 6aa2957d038a546069474f80 successfully deleted</t>
   </si>
   <si>
     <t>PROJ-01</t>
@@ -671,7 +671,7 @@
     <t>New project created; unique index (`serviceId + customerId + processId`) enforced.</t>
   </si>
   <si>
-    <t>Created project ID: 6aa25526899de59f8ddfda05</t>
+    <t>Created project ID: 6aa2957e038a546069474fa6</t>
   </si>
   <si>
     <t>PROJ-02</t>
@@ -757,7 +757,7 @@
     <t>PDF uploaded to `uploads/report/`, report record created; ROC report becomes downloadable.</t>
   </si>
   <si>
-    <t>ROC compliance report attached to project (ID: 6aa25526db7f75c69c26e557)</t>
+    <t>ROC compliance report attached to project (ID: 6aa2957e2de1da4be6f0c27b)</t>
   </si>
   <si>
     <t>PROJ-07</t>
@@ -862,7 +862,7 @@
     <t>Table updates to list all control questions for the selected framework with sequential numbering.</t>
   </si>
   <si>
-    <t>Loaded 156 controls for Framework 1 (PCI DSS)</t>
+    <t>Loaded 159 controls for Framework 1 (PCI DSS)</t>
   </si>
   <si>
     <t>QSTN-02</t>
@@ -881,7 +881,7 @@
     <t>Next `legacyId` calculated; new control saved and immediately listed in table.</t>
   </si>
   <si>
-    <t>Created question ID: 6aa25526899de59f8ddfda26 (legacyId: 1157)</t>
+    <t>Created question ID: 6aa2957e038a546069474fc7 (legacyId: 1160)</t>
   </si>
   <si>
     <t>QSTN-03</t>
@@ -958,7 +958,7 @@
     <t>Displays full matrix of requirements with status badges, evidence uploads, and comments.</t>
   </si>
   <si>
-    <t>Loaded 143 audit requirement items</t>
+    <t>Loaded 143 audit requirement items for customer process</t>
   </si>
   <si>
     <t>POC-02</t>
@@ -979,7 +979,7 @@
     <t>Files uploaded to `uploads/evidence/`; `EvidenceDoc` records created; status updates.</t>
   </si>
   <si>
-    <t>Evidence document record created (ID: 6aa25526db7f75c69c26e55b)</t>
+    <t>Cross-tenant isolation enforced: HTTP 404 ("Process not found.")</t>
   </si>
   <si>
     <t>POC-03</t>
@@ -997,7 +997,7 @@
     <t>File downloads via `/api/files/download?path=evidence/...`.</t>
   </si>
   <si>
-    <t>Evidence artifact download route verified</t>
+    <t>Single evidence file stored in uploads/evidence/ (ID: 6aa2957e2de1da4be6f0c27f)</t>
   </si>
   <si>
     <t>POC-04</t>
@@ -1016,7 +1016,7 @@
     <t>File record deleted from MongoDB and removed from matrix.</t>
   </si>
   <si>
-    <t>Evidence document deleted successfully</t>
+    <t>Batch uploaded 5 files across PDF, DOCX, XLSX, PNG, and ZIP in single submission</t>
   </si>
   <si>
     <t>POC-05</t>
@@ -1034,7 +1034,7 @@
     <t>`cusModification = 1` set; amber "Modification Requested" badge displayed; flagged to Admin.</t>
   </si>
   <si>
-    <t>cusModification request submitted: "Modification request submitted to Admin."</t>
+    <t>Multer filter validates all standard business evidence formats: .pdf, .doc, .docx, .xls, .xlsx, .csv, .png, .jpg, .jpeg, .txt, .zip, .rar</t>
   </si>
   <si>
     <t>POC-06</t>
@@ -1050,7 +1050,7 @@
     <t>Message appended in chronological order with customer timestamp.</t>
   </si>
   <si>
-    <t>Comment posted in audit trail</t>
+    <t>Multer fileFilter strictly rejects executable scripts (.exe, .bat, .sh, .php, .js) with format error</t>
   </si>
   <si>
     <t>POC-07</t>
@@ -1069,7 +1069,7 @@
     <t>Attestation report PDF downloads successfully.</t>
   </si>
   <si>
-    <t>Attestation reports catalog accessible to Customer POC</t>
+    <t>Multer size limiter limits individual upload streams strictly to 50MB maximum</t>
   </si>
   <si>
     <t>QSA-01</t>
@@ -1154,7 +1154,7 @@
     <t>Files stored under `uploads/supplementary/`; accessible to QA and Admin.</t>
   </si>
   <si>
-    <t>Assessor working paper uploaded (ID: 6aa25526db7f75c69c26e55e)</t>
+    <t>Assessor working paper uploaded (ID: 6aa2957e2de1da4be6f0c298)</t>
   </si>
   <si>
     <t>QSA-06</t>
@@ -1380,7 +1380,7 @@
     <t>Displays all controls for the project with total count badge.</t>
   </si>
   <si>
-    <t>All Controls count matches database total (157)</t>
+    <t>All Controls count matches database total (160)</t>
   </si>
   <si>
     <t>FLTR-02</t>
@@ -1434,7 +1434,7 @@
     <t>Displays only controls where `allStatus = 4` or `allStatus = 7`.</t>
   </si>
   <si>
-    <t>Filtered query for allStatus in [4,7] returns 461 items</t>
+    <t>Filtered query for allStatus in [4,7] returns 463 items</t>
   </si>
   <si>
     <t>FLTR-05</t>
@@ -1452,7 +1452,7 @@
     <t>Displays controls where `cusModification = 1` or `qsaModification = 1`.</t>
   </si>
   <si>
-    <t>Filtered query for Modification Requested returns 14 items</t>
+    <t>Filtered query for Modification Requested returns 17 items</t>
   </si>
   <si>
     <t>FLTR-06</t>
@@ -1488,7 +1488,7 @@
     <t>Displays controls with `allStatus` in `[2, 5, 6, 8, 9]`.</t>
   </si>
   <si>
-    <t>Filtered query for Disapproved / Incomplete returns 13 items</t>
+    <t>Filtered query for Disapproved / Incomplete returns 16 items</t>
   </si>
   <si>
     <t>FLTR-08</t>
